--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="G2">
-        <v>401</v>
+        <v>195</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>144</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="G3">
-        <v>414</v>
+        <v>188</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>79</v>
       </c>
       <c r="D2">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E2">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="G2">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D3">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G3">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="H3">
         <v>426</v>
